--- a/data/simpanan_pengajuan.xlsx
+++ b/data/simpanan_pengajuan.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -556,6 +556,66 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>f7c9ca5b-0eee-4a76-8e69-e94a651f9922</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-04-27 16:12:01</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Simpanan Hari Raya</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pengajuan Simpanan Hari Raya menunggu konfirmasi admin</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-04-27 16:12:50</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>septiawan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/simpanan_pengajuan.xlsx
+++ b/data/simpanan_pengajuan.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -616,6 +616,58 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6ad542f6-10c1-4883-9e09-5e56542fe6f7</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-04-28 11:29:54</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Simpanan Hari Raya</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Pengajuan Simpanan Hari Raya menunggu konfirmasi admin</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Menunggu</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>septiawan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/simpanan_pengajuan.xlsx
+++ b/data/simpanan_pengajuan.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
@@ -668,6 +668,58 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>30b7cf48-57f9-43af-bd1f-9f18697f1418</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-04-28 16:29:33</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Simpanan Manasuka</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pengajuan Simpanan Manasuka menunggu konfirmasi admin</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Menunggu</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>septiawan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/simpanan_pengajuan.xlsx
+++ b/data/simpanan_pengajuan.xlsx
@@ -417,19 +417,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -499,224 +499,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5f6c6bff-17c2-4552-a648-0a9af869c9d6</t>
+          <t>c41c07a9-e6a6-4253-8f80-072c1ad0e727</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+          <t>AGT-DEMO-001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AGT-001</t>
+          <t>KOP-0001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Septiawan</t>
+          <t>Anggota Demo</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-04-23 15:57:06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Simpanan Hari Raya</t>
+          <t>Manasuka</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pengajuan Simpanan Hari Raya menunggu konfirmasi admin</t>
+          <t>Pengajuan setoran dari anggota</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Disetujui</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2026-04-23 15:57:21</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
+          <t>Menunggu</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>septiawan</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>f7c9ca5b-0eee-4a76-8e69-e94a651f9922</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AGT-001</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Septiawan</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-04-27 16:12:01</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Simpanan Hari Raya</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>250000</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Pengajuan Simpanan Hari Raya menunggu konfirmasi admin</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Disetujui</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-04-27 16:12:50</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>septiawan</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>6ad542f6-10c1-4883-9e09-5e56542fe6f7</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AGT-001</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Septiawan</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-04-28 11:29:54</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Simpanan Hari Raya</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Pengajuan Simpanan Hari Raya menunggu konfirmasi admin</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Menunggu</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>septiawan</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>30b7cf48-57f9-43af-bd1f-9f18697f1418</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AGT-001</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Septiawan</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-04-28 16:29:33</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Simpanan Manasuka</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>45000000</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Pengajuan Simpanan Manasuka menunggu konfirmasi admin</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Menunggu</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>septiawan</t>
+          <t>anggota_demo</t>
         </is>
       </c>
     </row>

--- a/data/simpanan_pengajuan.xlsx
+++ b/data/simpanan_pengajuan.xlsx
@@ -417,19 +417,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -499,50 +499,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>c41c07a9-e6a6-4253-8f80-072c1ad0e727</t>
+          <t>5f6a01ff-3074-4782-8834-6561ad209205</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-05-04 10:33:23</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Simpanan Pensiun</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Pengajuan Simpanan Pensiun menunggu konfirmasi admin</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-05-04 10:39:21</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>admin_koperasi</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>boseng</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>33e02c95-cdb3-4a53-9e34-93d37b91795c</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>AGT-DEMO-001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>KOP-0001</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Anggota Demo</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Manasuka</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="G3" t="n">
         <v>200000</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Pengajuan setoran dari anggota</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Menunggu</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>anggota_demo</t>
         </is>

--- a/data/simpanan_pengajuan.xlsx
+++ b/data/simpanan_pengajuan.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -425,7 +425,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
@@ -608,6 +608,110 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cd59aa05-5ff2-4fbe-9bdf-704d59c60b0a</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-05-08 11:26:27</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Simpanan Wajib</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Pengajuan Simpanan Wajib menunggu konfirmasi admin</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Menunggu</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>boseng</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0e6f3bd5-7b0f-4600-a6a8-d22fe75bbbde</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-05-08 11:26:51</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Simpanan Hari Raya</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pengajuan Simpanan Hari Raya menunggu konfirmasi admin</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Menunggu</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>boseng</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/simpanan_pengajuan.xlsx
+++ b/data/simpanan_pengajuan.xlsx
@@ -417,19 +417,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -496,222 +496,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>5f6a01ff-3074-4782-8834-6561ad209205</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AGT-001</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Boseng</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-05-04 10:33:23</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Simpanan Pensiun</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>500000</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Pengajuan Simpanan Pensiun menunggu konfirmasi admin</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Disetujui</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2026-05-04 10:39:21</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>admin_koperasi</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>boseng</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>33e02c95-cdb3-4a53-9e34-93d37b91795c</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AGT-DEMO-001</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>KOP-0001</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Anggota Demo</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Manasuka</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>200000</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Pengajuan setoran dari anggota</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Menunggu</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>anggota_demo</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cd59aa05-5ff2-4fbe-9bdf-704d59c60b0a</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AGT-001</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Boseng</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-05-08 11:26:27</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Simpanan Wajib</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Pengajuan Simpanan Wajib menunggu konfirmasi admin</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Menunggu</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>boseng</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>0e6f3bd5-7b0f-4600-a6a8-d22fe75bbbde</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AGT-001</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Boseng</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-05-08 11:26:51</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Simpanan Hari Raya</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>500000</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Pengajuan Simpanan Hari Raya menunggu konfirmasi admin</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Menunggu</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>boseng</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
